--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635438</v>
+        <v>121635436</v>
       </c>
       <c r="B2" t="n">
-        <v>94877</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>588042</v>
       </c>
       <c r="R2" t="n">
-        <v>6511511</v>
+        <v>6511486</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635437</v>
+        <v>121635438</v>
       </c>
       <c r="B3" t="n">
-        <v>94877</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588101</v>
+        <v>587786</v>
       </c>
       <c r="R3" t="n">
-        <v>6511495</v>
+        <v>6511511</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635436</v>
+        <v>121635437</v>
       </c>
       <c r="B4" t="n">
-        <v>94877</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588042</v>
+        <v>588101</v>
       </c>
       <c r="R4" t="n">
-        <v>6511486</v>
+        <v>6511495</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635436</v>
+        <v>121635438</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588042</v>
+        <v>587786</v>
       </c>
       <c r="R2" t="n">
-        <v>6511486</v>
+        <v>6511511</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635438</v>
+        <v>121635437</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587786</v>
+        <v>588101</v>
       </c>
       <c r="R3" t="n">
-        <v>6511511</v>
+        <v>6511495</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635437</v>
+        <v>121635436</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588101</v>
+        <v>588042</v>
       </c>
       <c r="R4" t="n">
-        <v>6511495</v>
+        <v>6511486</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635438</v>
+        <v>121635437</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>588101</v>
       </c>
       <c r="R2" t="n">
-        <v>6511511</v>
+        <v>6511495</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635437</v>
+        <v>121635438</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588101</v>
+        <v>587786</v>
       </c>
       <c r="R3" t="n">
-        <v>6511495</v>
+        <v>6511511</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635437</v>
+        <v>121635438</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588101</v>
+        <v>587786</v>
       </c>
       <c r="R2" t="n">
-        <v>6511495</v>
+        <v>6511511</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635438</v>
+        <v>121635436</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587786</v>
+        <v>588042</v>
       </c>
       <c r="R3" t="n">
-        <v>6511511</v>
+        <v>6511486</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635436</v>
+        <v>121635437</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588042</v>
+        <v>588101</v>
       </c>
       <c r="R4" t="n">
-        <v>6511486</v>
+        <v>6511495</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635436</v>
+        <v>121635437</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588042</v>
+        <v>588101</v>
       </c>
       <c r="R3" t="n">
-        <v>6511486</v>
+        <v>6511495</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635437</v>
+        <v>121635436</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588101</v>
+        <v>588042</v>
       </c>
       <c r="R4" t="n">
-        <v>6511495</v>
+        <v>6511486</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635437</v>
+        <v>121635436</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588101</v>
+        <v>588042</v>
       </c>
       <c r="R3" t="n">
-        <v>6511495</v>
+        <v>6511486</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635436</v>
+        <v>121635437</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588042</v>
+        <v>588101</v>
       </c>
       <c r="R4" t="n">
-        <v>6511486</v>
+        <v>6511495</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635438</v>
+        <v>121635437</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>588101</v>
       </c>
       <c r="R2" t="n">
-        <v>6511511</v>
+        <v>6511495</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121635437</v>
+        <v>121635438</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588101</v>
+        <v>587786</v>
       </c>
       <c r="R4" t="n">
-        <v>6511495</v>
+        <v>6511511</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59214-2024 artfynd.xlsx
+++ b/artfynd/A 59214-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121635437</v>
+        <v>121635436</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588101</v>
+        <v>588042</v>
       </c>
       <c r="R2" t="n">
-        <v>6511495</v>
+        <v>6511486</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121635436</v>
+        <v>121635437</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588042</v>
+        <v>588101</v>
       </c>
       <c r="R3" t="n">
-        <v>6511486</v>
+        <v>6511495</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>121635438</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
